--- a/data/nzd0503/nzd0503.xlsx
+++ b/data/nzd0503/nzd0503.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H396"/>
+  <dimension ref="A1:H399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12213,7 +12213,7 @@
         <v>248.6</v>
       </c>
       <c r="C394" t="n">
-        <v>314.46</v>
+        <v>328.7</v>
       </c>
       <c r="D394" t="n">
         <v>328.56</v>
@@ -12243,7 +12243,7 @@
         <v>231.73</v>
       </c>
       <c r="C395" t="n">
-        <v>297.82</v>
+        <v>325.79</v>
       </c>
       <c r="D395" t="n">
         <v>323.02</v>
@@ -12273,7 +12273,7 @@
         <v>214.14</v>
       </c>
       <c r="C396" t="n">
-        <v>281.98</v>
+        <v>324.97</v>
       </c>
       <c r="D396" t="n">
         <v>320.82</v>
@@ -12288,6 +12288,96 @@
         <v>398.69</v>
       </c>
       <c r="H396" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>214.14</v>
+      </c>
+      <c r="C397" t="n">
+        <v>323.78</v>
+      </c>
+      <c r="D397" t="n">
+        <v>320.33</v>
+      </c>
+      <c r="E397" t="n">
+        <v>319.66</v>
+      </c>
+      <c r="F397" t="n">
+        <v>323.44</v>
+      </c>
+      <c r="G397" t="n">
+        <v>398.07</v>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>197.9</v>
+      </c>
+      <c r="C398" t="n">
+        <v>304.7</v>
+      </c>
+      <c r="D398" t="n">
+        <v>319.15</v>
+      </c>
+      <c r="E398" t="n">
+        <v>319.32</v>
+      </c>
+      <c r="F398" t="n">
+        <v>322.81</v>
+      </c>
+      <c r="G398" t="n">
+        <v>399.89</v>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>195.3</v>
+      </c>
+      <c r="C399" t="n">
+        <v>291.39</v>
+      </c>
+      <c r="D399" t="n">
+        <v>317.77</v>
+      </c>
+      <c r="E399" t="n">
+        <v>318.26</v>
+      </c>
+      <c r="F399" t="n">
+        <v>321.9</v>
+      </c>
+      <c r="G399" t="n">
+        <v>399.27</v>
+      </c>
+      <c r="H399" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12304,7 +12394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B457"/>
+  <dimension ref="A1:B460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16877,6 +16967,36 @@
       </c>
       <c r="B457" t="n">
         <v>-0.74</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
@@ -17045,28 +17165,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.01956863610354</v>
+        <v>-1.136089947323828</v>
       </c>
       <c r="J2" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K2" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02505524985601015</v>
+        <v>0.03071878152122198</v>
       </c>
       <c r="M2" t="n">
-        <v>35.551698322394</v>
+        <v>35.93666254184465</v>
       </c>
       <c r="N2" t="n">
-        <v>1859.519776917091</v>
+        <v>1886.260080124867</v>
       </c>
       <c r="O2" t="n">
-        <v>43.12214949323713</v>
+        <v>43.43109577393676</v>
       </c>
       <c r="P2" t="n">
-        <v>302.8857649046988</v>
+        <v>304.3441294584266</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17123,28 +17243,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.830462989728261</v>
+        <v>-1.756309376657814</v>
       </c>
       <c r="J3" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K3" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1632617110217155</v>
+        <v>0.1520463115853764</v>
       </c>
       <c r="M3" t="n">
-        <v>19.9730202441859</v>
+        <v>20.07131185821756</v>
       </c>
       <c r="N3" t="n">
-        <v>808.6041477390844</v>
+        <v>816.1395924561261</v>
       </c>
       <c r="O3" t="n">
-        <v>28.43596574303543</v>
+        <v>28.568156966387</v>
       </c>
       <c r="P3" t="n">
-        <v>335.7378897575816</v>
+        <v>334.8280252279091</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17201,28 +17321,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8838373534703617</v>
+        <v>-0.8646641254509924</v>
       </c>
       <c r="J4" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K4" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2375204832251133</v>
+        <v>0.2306074241713106</v>
       </c>
       <c r="M4" t="n">
-        <v>8.736302112889698</v>
+        <v>8.778133533285576</v>
       </c>
       <c r="N4" t="n">
-        <v>117.8766670667955</v>
+        <v>118.1406357274926</v>
       </c>
       <c r="O4" t="n">
-        <v>10.85710214867648</v>
+        <v>10.86925184764308</v>
       </c>
       <c r="P4" t="n">
-        <v>330.3662561217057</v>
+        <v>330.130440332536</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17279,28 +17399,28 @@
         <v>0.0806</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.727823780636947</v>
+        <v>-0.7129222465108063</v>
       </c>
       <c r="J5" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K5" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L5" t="n">
-        <v>0.244086145024849</v>
+        <v>0.2376331998469087</v>
       </c>
       <c r="M5" t="n">
-        <v>7.002258799771615</v>
+        <v>7.033112742464509</v>
       </c>
       <c r="N5" t="n">
-        <v>77.11479179569862</v>
+        <v>77.22731020634721</v>
       </c>
       <c r="O5" t="n">
-        <v>8.781502821026628</v>
+        <v>8.787907043565449</v>
       </c>
       <c r="P5" t="n">
-        <v>328.9478496428978</v>
+        <v>328.7645666949358</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17357,28 +17477,28 @@
         <v>0.059</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6119920035931048</v>
+        <v>-0.5998354413274959</v>
       </c>
       <c r="J6" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K6" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1970624109503455</v>
+        <v>0.1921249153962521</v>
       </c>
       <c r="M6" t="n">
-        <v>6.724980009753123</v>
+        <v>6.736802706511375</v>
       </c>
       <c r="N6" t="n">
-        <v>71.73407844401595</v>
+        <v>71.65631756487875</v>
       </c>
       <c r="O6" t="n">
-        <v>8.46959730117176</v>
+        <v>8.465005467504362</v>
       </c>
       <c r="P6" t="n">
-        <v>331.2595204887123</v>
+        <v>331.1100032595065</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17435,28 +17555,28 @@
         <v>0.1629</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3659029920737821</v>
+        <v>-0.3460561819315983</v>
       </c>
       <c r="J7" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K7" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08553130035289847</v>
+        <v>0.07697748002173166</v>
       </c>
       <c r="M7" t="n">
-        <v>6.608619871175023</v>
+        <v>6.650409211551398</v>
       </c>
       <c r="N7" t="n">
-        <v>67.2870862481935</v>
+        <v>68.00980770437359</v>
       </c>
       <c r="O7" t="n">
-        <v>8.202870610231122</v>
+        <v>8.246805909221678</v>
       </c>
       <c r="P7" t="n">
-        <v>396.0105036778326</v>
+        <v>395.7663685738768</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17494,7 +17614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H396"/>
+  <dimension ref="A1:H399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33956,7 +34076,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>-45.78872915500259,170.74076037347277</t>
+          <t>-45.78876426710537,170.74093649906453</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -33998,7 +34118,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>-45.78868812479045,170.74055456408504</t>
+          <t>-45.788757091830846,170.74090050708844</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -34040,7 +34160,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>-45.78864906684501,170.7403586496724</t>
+          <t>-45.78875506993016,170.74089036502133</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -34064,6 +34184,132 @@
         </is>
       </c>
       <c r="H396" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>-45.78786313576798,170.73976794347854</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>-45.78875213570688,170.74087564665697</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>-45.78935380631152,170.74061487160753</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-45.7899596589843,170.74038923462018</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>-45.79058033091585,170.74021406756972</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>-45.79133143097853,170.7409937540044</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>-45.78782109456232,170.7395679201958</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>-45.788705089249405,170.74063965831292</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>-45.789351041471626,170.74060021939923</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>-45.78995885652275,170.74038501500192</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>-45.7905790207264,170.74020618445203</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>-45.791334668550114,170.74101669958682</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>-45.787814363795384,170.73953589679292</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>-45.788672269868954,170.74047503566214</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>-45.78934780801246,170.74058308376777</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>-45.7899563547299,170.74037185972227</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>-45.790577128229586,170.74019479772716</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>-45.79133356564163,170.7410088829595</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0503/nzd0503.xlsx
+++ b/data/nzd0503/nzd0503.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H399"/>
+  <dimension ref="A1:H402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12333,7 +12333,7 @@
         <v>197.9</v>
       </c>
       <c r="C398" t="n">
-        <v>304.7</v>
+        <v>321.49</v>
       </c>
       <c r="D398" t="n">
         <v>319.15</v>
@@ -12363,7 +12363,7 @@
         <v>195.3</v>
       </c>
       <c r="C399" t="n">
-        <v>291.39</v>
+        <v>321.49</v>
       </c>
       <c r="D399" t="n">
         <v>317.77</v>
@@ -12378,6 +12378,96 @@
         <v>399.27</v>
       </c>
       <c r="H399" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:14:11+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>192.56</v>
+      </c>
+      <c r="C400" t="n">
+        <v>317.63</v>
+      </c>
+      <c r="D400" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="E400" t="n">
+        <v>317.83</v>
+      </c>
+      <c r="F400" t="n">
+        <v>321.66</v>
+      </c>
+      <c r="G400" t="n">
+        <v>398.29</v>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>192.56</v>
+      </c>
+      <c r="C401" t="n">
+        <v>315.64</v>
+      </c>
+      <c r="D401" t="n">
+        <v>316.55</v>
+      </c>
+      <c r="E401" t="n">
+        <v>317.83</v>
+      </c>
+      <c r="F401" t="n">
+        <v>321.66</v>
+      </c>
+      <c r="G401" t="n">
+        <v>398.29</v>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>192.9</v>
+      </c>
+      <c r="C402" t="n">
+        <v>314.69</v>
+      </c>
+      <c r="D402" t="n">
+        <v>316.64</v>
+      </c>
+      <c r="E402" t="n">
+        <v>317.71</v>
+      </c>
+      <c r="F402" t="n">
+        <v>321.98</v>
+      </c>
+      <c r="G402" t="n">
+        <v>398.24</v>
+      </c>
+      <c r="H402" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12394,7 +12484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B460"/>
+  <dimension ref="A1:B463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16997,6 +17087,36 @@
       </c>
       <c r="B460" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -17165,28 +17285,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.136089947323828</v>
+        <v>-1.26349972537411</v>
       </c>
       <c r="J2" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K2" t="n">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03071878152122198</v>
+        <v>0.03731814672530875</v>
       </c>
       <c r="M2" t="n">
-        <v>35.93666254184465</v>
+        <v>36.37804684966083</v>
       </c>
       <c r="N2" t="n">
-        <v>1886.260080124867</v>
+        <v>1921.417306651412</v>
       </c>
       <c r="O2" t="n">
-        <v>43.43109577393676</v>
+        <v>43.83397434241404</v>
       </c>
       <c r="P2" t="n">
-        <v>304.3441294584266</v>
+        <v>305.9438252301717</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17243,28 +17363,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.756309376657814</v>
+        <v>-1.68953392719814</v>
       </c>
       <c r="J3" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K3" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1520463115853764</v>
+        <v>0.1425258975556836</v>
       </c>
       <c r="M3" t="n">
-        <v>20.07131185821756</v>
+        <v>20.16452806017011</v>
       </c>
       <c r="N3" t="n">
-        <v>816.1395924561261</v>
+        <v>820.7697361353326</v>
       </c>
       <c r="O3" t="n">
-        <v>28.568156966387</v>
+        <v>28.6490791498668</v>
       </c>
       <c r="P3" t="n">
-        <v>334.8280252279091</v>
+        <v>334.0049288358545</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17321,28 +17441,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8646641254509924</v>
+        <v>-0.849705007257764</v>
       </c>
       <c r="J4" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K4" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2306074241713106</v>
+        <v>0.2260177432617325</v>
       </c>
       <c r="M4" t="n">
-        <v>8.778133533285576</v>
+        <v>8.796408941423183</v>
       </c>
       <c r="N4" t="n">
-        <v>118.1406357274926</v>
+        <v>117.9681372952023</v>
       </c>
       <c r="O4" t="n">
-        <v>10.86925184764308</v>
+        <v>10.86131379231823</v>
       </c>
       <c r="P4" t="n">
-        <v>330.130440332536</v>
+        <v>329.9458356804336</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17399,28 +17519,28 @@
         <v>0.0806</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7129222465108063</v>
+        <v>-0.7004232929172453</v>
       </c>
       <c r="J5" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K5" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2376331998469087</v>
+        <v>0.2327888012870067</v>
       </c>
       <c r="M5" t="n">
-        <v>7.033112742464509</v>
+        <v>7.050167331334642</v>
       </c>
       <c r="N5" t="n">
-        <v>77.22731020634721</v>
+        <v>77.14608769085862</v>
       </c>
       <c r="O5" t="n">
-        <v>8.787907043565449</v>
+        <v>8.78328456164655</v>
       </c>
       <c r="P5" t="n">
-        <v>328.7645666949358</v>
+        <v>328.6103218253335</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17477,28 +17597,28 @@
         <v>0.059</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5998354413274959</v>
+        <v>-0.5894827777858173</v>
       </c>
       <c r="J6" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K6" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1921249153962521</v>
+        <v>0.1883204552751454</v>
       </c>
       <c r="M6" t="n">
-        <v>6.736802706511375</v>
+        <v>6.739102941157035</v>
       </c>
       <c r="N6" t="n">
-        <v>71.65631756487875</v>
+        <v>71.46102564281253</v>
       </c>
       <c r="O6" t="n">
-        <v>8.465005467504362</v>
+        <v>8.453462346447905</v>
       </c>
       <c r="P6" t="n">
-        <v>331.1100032595065</v>
+        <v>330.9822410304923</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17555,28 +17675,28 @@
         <v>0.1629</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3460561819315983</v>
+        <v>-0.3281045986971092</v>
       </c>
       <c r="J7" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K7" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07697748002173166</v>
+        <v>0.06973050803086922</v>
       </c>
       <c r="M7" t="n">
-        <v>6.650409211551398</v>
+        <v>6.685350183846116</v>
       </c>
       <c r="N7" t="n">
-        <v>68.00980770437359</v>
+        <v>68.52522665115131</v>
       </c>
       <c r="O7" t="n">
-        <v>8.246805909221678</v>
+        <v>8.27799653606785</v>
       </c>
       <c r="P7" t="n">
-        <v>395.7663685738768</v>
+        <v>395.5448340912679</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17614,7 +17734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H399"/>
+  <dimension ref="A1:H402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34244,7 +34364,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>-45.788705089249405,170.74063965831292</t>
+          <t>-45.78874648917106,170.74084732308648</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -34286,7 +34406,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>-45.788672269868954,170.74047503566214</t>
+          <t>-45.78874648917106,170.74084732308648</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -34310,6 +34430,132 @@
         </is>
       </c>
       <c r="H399" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:14:11+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>-45.78780727059297,170.73950214906165</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>-45.788736971413805,170.74079958118634</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>-45.789345722664265,170.7405720325283</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>-45.78995533985124,170.74036652314695</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>-45.79057662910937,170.740191794635</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>-45.79133182233359,170.74099652764608</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>-45.78780727059297,170.73950214906165</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>-45.78873206458308,170.74077496814084</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>-45.78934494944501,170.7405679348779</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>-45.78995533985124,170.74036652314695</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>-45.79057662910937,170.740191794635</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>-45.79133182233359,170.74099652764608</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>-45.7878081507719,170.73950633673584</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>-45.78872972212435,170.7407632181961</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>-45.78934516032299,170.7405690524189</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>-45.78995505662925,170.74036503387015</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>-45.79057729460298,170.7401957987579</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>-45.79133173338926,170.74099589727297</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0503/nzd0503.xlsx
+++ b/data/nzd0503/nzd0503.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H402"/>
+  <dimension ref="A1:H404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12468,6 +12468,66 @@
         <v>398.24</v>
       </c>
       <c r="H402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>201.06</v>
+      </c>
+      <c r="C403" t="n">
+        <v>316.55</v>
+      </c>
+      <c r="D403" t="n">
+        <v>317.93</v>
+      </c>
+      <c r="E403" t="n">
+        <v>318.51</v>
+      </c>
+      <c r="F403" t="n">
+        <v>322.42</v>
+      </c>
+      <c r="G403" t="n">
+        <v>398.56</v>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>190.49</v>
+      </c>
+      <c r="C404" t="n">
+        <v>316.05</v>
+      </c>
+      <c r="D404" t="n">
+        <v>317.79</v>
+      </c>
+      <c r="E404" t="n">
+        <v>319.41</v>
+      </c>
+      <c r="F404" t="n">
+        <v>323.55</v>
+      </c>
+      <c r="G404" t="n">
+        <v>400.91</v>
+      </c>
+      <c r="H404" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12484,7 +12544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B463"/>
+  <dimension ref="A1:B465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17117,6 +17177,26 @@
       </c>
       <c r="B463" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -17285,28 +17365,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.26349972537411</v>
+        <v>-1.342724635265515</v>
       </c>
       <c r="J2" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K2" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03731814672530875</v>
+        <v>0.04173159852369301</v>
       </c>
       <c r="M2" t="n">
-        <v>36.37804684966083</v>
+        <v>36.6440117080024</v>
       </c>
       <c r="N2" t="n">
-        <v>1921.417306651412</v>
+        <v>1940.934116714945</v>
       </c>
       <c r="O2" t="n">
-        <v>43.83397434241404</v>
+        <v>44.05603382869304</v>
       </c>
       <c r="P2" t="n">
-        <v>305.9438252301717</v>
+        <v>306.9423637451756</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17363,28 +17443,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.68953392719814</v>
+        <v>-1.661398619853809</v>
       </c>
       <c r="J3" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K3" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1425258975556836</v>
+        <v>0.1390889097226251</v>
       </c>
       <c r="M3" t="n">
-        <v>20.16452806017011</v>
+        <v>20.16931263318459</v>
       </c>
       <c r="N3" t="n">
-        <v>820.7697361353326</v>
+        <v>820.5227429286634</v>
       </c>
       <c r="O3" t="n">
-        <v>28.6490791498668</v>
+        <v>28.6447681597995</v>
       </c>
       <c r="P3" t="n">
-        <v>334.0049288358545</v>
+        <v>333.656514872325</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17441,28 +17521,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.849705007257764</v>
+        <v>-0.8387473125104864</v>
       </c>
       <c r="J4" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K4" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2260177432617325</v>
+        <v>0.2223624152239575</v>
       </c>
       <c r="M4" t="n">
-        <v>8.796408941423183</v>
+        <v>8.814053640073205</v>
       </c>
       <c r="N4" t="n">
-        <v>117.9681372952023</v>
+        <v>117.9629163392154</v>
       </c>
       <c r="O4" t="n">
-        <v>10.86131379231823</v>
+        <v>10.86107344322905</v>
       </c>
       <c r="P4" t="n">
-        <v>329.9458356804336</v>
+        <v>329.8101061071827</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17519,28 +17599,28 @@
         <v>0.0806</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7004232929172453</v>
+        <v>-0.691076460746948</v>
       </c>
       <c r="J5" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K5" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2327888012870067</v>
+        <v>0.2287959369713896</v>
       </c>
       <c r="M5" t="n">
-        <v>7.050167331334642</v>
+        <v>7.067167006241253</v>
       </c>
       <c r="N5" t="n">
-        <v>77.14608769085862</v>
+        <v>77.186359754504</v>
       </c>
       <c r="O5" t="n">
-        <v>8.78328456164655</v>
+        <v>8.785576802606872</v>
       </c>
       <c r="P5" t="n">
-        <v>328.6103218253335</v>
+        <v>328.4945369094789</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17597,28 +17677,28 @@
         <v>0.059</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5894827777858173</v>
+        <v>-0.5814918039313191</v>
       </c>
       <c r="J6" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K6" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1883204552751454</v>
+        <v>0.1850145377063623</v>
       </c>
       <c r="M6" t="n">
-        <v>6.739102941157035</v>
+        <v>6.745864450555111</v>
       </c>
       <c r="N6" t="n">
-        <v>71.46102564281253</v>
+        <v>71.41649960438497</v>
       </c>
       <c r="O6" t="n">
-        <v>8.453462346447905</v>
+        <v>8.450828338357429</v>
       </c>
       <c r="P6" t="n">
-        <v>330.9822410304923</v>
+        <v>330.8832489282207</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17675,28 +17755,28 @@
         <v>0.1629</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3281045986971092</v>
+        <v>-0.3149634296667106</v>
       </c>
       <c r="J7" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K7" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06973050803086922</v>
+        <v>0.06446645223614533</v>
       </c>
       <c r="M7" t="n">
-        <v>6.685350183846116</v>
+        <v>6.716877011669028</v>
       </c>
       <c r="N7" t="n">
-        <v>68.52522665115131</v>
+        <v>69.02608062985797</v>
       </c>
       <c r="O7" t="n">
-        <v>8.27799653606785</v>
+        <v>8.308193584038468</v>
       </c>
       <c r="P7" t="n">
-        <v>395.5448340912679</v>
+        <v>395.3820377430023</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17734,7 +17814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H402"/>
+  <dimension ref="A1:H404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34561,6 +34641,90 @@
         </is>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>-45.78782927502102,170.7396068409578</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>-45.78873430841083,170.74078622335205</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>-45.78934818290641,170.74058507050754</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>-45.78995694477552,170.74037496238245</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>-45.79057820965649,170.74020130442696</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>-45.791332302632874,170.74099993166092</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>-45.78780191185323,170.73947665351878</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>-45.78873307553858,170.74078003916995</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>-45.789347854874215,170.74058333211025</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>-45.78995906893906,170.74038613195967</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>-45.79058055967903,170.74021544398713</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>-45.7913364830113,170.7410295592002</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
